--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -470,28 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.73611</v>
+        <v>16.40158</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47637</v>
+        <v>16.95271</v>
       </c>
       <c r="E2" t="n">
-        <v>16.73493</v>
+        <v>16.49567</v>
       </c>
       <c r="F2" t="n">
-        <v>54.36854</v>
+        <v>43.16873</v>
       </c>
       <c r="G2" t="n">
-        <v>41.38244</v>
+        <v>0.05071</v>
       </c>
       <c r="H2" t="n">
-        <v>85.02527000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05108</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.83541</v>
+        <v>1.83715</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.60207</v>
+        <v>17.13256</v>
       </c>
       <c r="D3" t="n">
-        <v>16.52926</v>
+        <v>16.64823</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58704</v>
+        <v>16.87742</v>
       </c>
       <c r="F3" t="n">
-        <v>56.0993</v>
+        <v>4276.462</v>
       </c>
       <c r="G3" t="n">
-        <v>42.99204</v>
+        <v>0.05078</v>
       </c>
       <c r="H3" t="n">
-        <v>85.49879</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.80138</v>
+        <v>1.8079</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.93977</v>
+        <v>16.92506</v>
       </c>
       <c r="D4" t="n">
-        <v>16.71745</v>
+        <v>16.66203</v>
       </c>
       <c r="E4" t="n">
-        <v>16.68631</v>
+        <v>16.76261</v>
       </c>
       <c r="F4" t="n">
-        <v>56.73142</v>
+        <v>42.92982</v>
       </c>
       <c r="G4" t="n">
-        <v>42.10789</v>
+        <v>0.05106</v>
       </c>
       <c r="H4" t="n">
-        <v>85.38381</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05064</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.83009</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.69017</v>
+        <v>16.93139</v>
       </c>
       <c r="D5" t="n">
-        <v>16.68019</v>
+        <v>16.50325</v>
       </c>
       <c r="E5" t="n">
-        <v>16.50661</v>
+        <v>16.73792</v>
       </c>
       <c r="F5" t="n">
-        <v>56.97373</v>
+        <v>42.22525</v>
       </c>
       <c r="G5" t="n">
-        <v>42.03851</v>
+        <v>0.051</v>
       </c>
       <c r="H5" t="n">
-        <v>83.70833</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04987</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.83205</v>
+        <v>1.84323</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.6045</v>
+        <v>16.85025</v>
       </c>
       <c r="D6" t="n">
-        <v>16.63316</v>
+        <v>16.55049</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53267</v>
+        <v>16.81305</v>
       </c>
       <c r="F6" t="n">
-        <v>55.52875</v>
+        <v>42.33227</v>
       </c>
       <c r="G6" t="n">
-        <v>42.37238</v>
+        <v>0.0521</v>
       </c>
       <c r="H6" t="n">
-        <v>84.91379999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.80652</v>
+        <v>1.84833</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.59365</v>
+        <v>16.94666</v>
       </c>
       <c r="D7" t="n">
-        <v>16.721</v>
+        <v>16.38961</v>
       </c>
       <c r="E7" t="n">
-        <v>17.07151</v>
+        <v>16.90444</v>
       </c>
       <c r="F7" t="n">
-        <v>55.97431</v>
+        <v>42.34757</v>
       </c>
       <c r="G7" t="n">
-        <v>42.28574</v>
+        <v>0.04959</v>
       </c>
       <c r="H7" t="n">
-        <v>85.42878</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05032</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.75639</v>
+        <v>1.82704</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.72797</v>
+        <v>16.53865</v>
       </c>
       <c r="D8" t="n">
-        <v>16.46906</v>
+        <v>16.37098</v>
       </c>
       <c r="E8" t="n">
-        <v>16.98937</v>
+        <v>16.51382</v>
       </c>
       <c r="F8" t="n">
-        <v>54.57397</v>
+        <v>42.96685</v>
       </c>
       <c r="G8" t="n">
-        <v>42.53885</v>
+        <v>0.05143</v>
       </c>
       <c r="H8" t="n">
-        <v>83.94658</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05043</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.80726</v>
+        <v>1.79295</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.39756</v>
+        <v>16.76084</v>
       </c>
       <c r="D9" t="n">
-        <v>16.80115</v>
+        <v>16.47336</v>
       </c>
       <c r="E9" t="n">
-        <v>16.80951</v>
+        <v>16.48894</v>
       </c>
       <c r="F9" t="n">
-        <v>54.90855</v>
+        <v>43.1087</v>
       </c>
       <c r="G9" t="n">
-        <v>42.30112</v>
+        <v>0.05012</v>
       </c>
       <c r="H9" t="n">
-        <v>83.7835</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.04929</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.81111</v>
+        <v>1.80226</v>
       </c>
     </row>
     <row r="10">
@@ -718,67 +660,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.98527</v>
+        <v>16.55488</v>
       </c>
       <c r="D10" t="n">
-        <v>16.8036</v>
+        <v>16.27847</v>
       </c>
       <c r="E10" t="n">
-        <v>16.99185</v>
+        <v>16.33616</v>
       </c>
       <c r="F10" t="n">
-        <v>55.84879</v>
+        <v>42.09953</v>
       </c>
       <c r="G10" t="n">
-        <v>42.21762</v>
+        <v>0.04979</v>
       </c>
       <c r="H10" t="n">
-        <v>85.81892999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.04962</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.86167</v>
+        <v>1.82761</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Outer Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Inner Radius</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -792,32 +698,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 2</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.14955</v>
+        <v>0.5966900000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>16.17479</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.79023</v>
-      </c>
-      <c r="F12" t="n">
-        <v>54.85228</v>
-      </c>
-      <c r="G12" t="n">
-        <v>42.68324</v>
-      </c>
-      <c r="H12" t="n">
-        <v>86.19279</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.78546</v>
+        <v>1.11657</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.80364</v>
+        <v>0.61563</v>
       </c>
       <c r="D13" t="n">
-        <v>16.53154</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.69683</v>
-      </c>
-      <c r="F13" t="n">
-        <v>55.60788</v>
-      </c>
-      <c r="G13" t="n">
-        <v>42.47549</v>
-      </c>
-      <c r="H13" t="n">
-        <v>83.89857000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.04986</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.80639</v>
+        <v>1.12292</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.0247</v>
+        <v>0.59921</v>
       </c>
       <c r="D14" t="n">
-        <v>16.50844</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.74423</v>
-      </c>
-      <c r="F14" t="n">
-        <v>56.00941</v>
-      </c>
-      <c r="G14" t="n">
-        <v>42.94556</v>
-      </c>
-      <c r="H14" t="n">
-        <v>85.86068</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.05071</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.76652</v>
+        <v>1.09257</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.27017</v>
+        <v>0.61491</v>
       </c>
       <c r="D15" t="n">
-        <v>16.8562</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.76514</v>
-      </c>
-      <c r="F15" t="n">
-        <v>55.11756</v>
-      </c>
-      <c r="G15" t="n">
-        <v>41.77499</v>
-      </c>
-      <c r="H15" t="n">
-        <v>84.47008</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.81311</v>
+        <v>1.09332</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.31579</v>
+        <v>0.59355</v>
       </c>
       <c r="D16" t="n">
-        <v>16.61155</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.75319</v>
-      </c>
-      <c r="F16" t="n">
-        <v>55.14792</v>
-      </c>
-      <c r="G16" t="n">
-        <v>42.13333</v>
-      </c>
-      <c r="H16" t="n">
-        <v>85.52319</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.05067</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.81536</v>
+        <v>1.1243</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.37954</v>
+        <v>0.62583</v>
       </c>
       <c r="D17" t="n">
-        <v>16.98372</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.84433</v>
-      </c>
-      <c r="F17" t="n">
-        <v>55.93082</v>
-      </c>
-      <c r="G17" t="n">
-        <v>42.96777</v>
-      </c>
-      <c r="H17" t="n">
-        <v>83.91413</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05059</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.76358</v>
+        <v>1.12834</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.59702</v>
+        <v>0.61283</v>
       </c>
       <c r="D18" t="n">
-        <v>16.53322</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.92258</v>
-      </c>
-      <c r="F18" t="n">
-        <v>55.58312</v>
-      </c>
-      <c r="G18" t="n">
-        <v>43.19204</v>
-      </c>
-      <c r="H18" t="n">
-        <v>86.19452</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05082</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.76969</v>
+        <v>1.1194</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.77018</v>
+        <v>0.61429</v>
       </c>
       <c r="D19" t="n">
-        <v>16.40265</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.7604</v>
-      </c>
-      <c r="F19" t="n">
-        <v>54.69706</v>
-      </c>
-      <c r="G19" t="n">
-        <v>42.05693</v>
-      </c>
-      <c r="H19" t="n">
-        <v>85.20791</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05072</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.79089</v>
+        <v>1.08513</v>
       </c>
     </row>
     <row r="20">
@@ -1044,54 +806,51 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.95892</v>
+        <v>0.61356</v>
       </c>
       <c r="D20" t="n">
-        <v>16.34489</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.56672</v>
-      </c>
-      <c r="F20" t="n">
-        <v>55.45001</v>
-      </c>
-      <c r="G20" t="n">
-        <v>41.86196</v>
-      </c>
-      <c r="H20" t="n">
-        <v>83.60511</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05044</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.85016</v>
+        <v>1.11936</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Rz mean</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Rz min</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ra max</t>
         </is>
       </c>
     </row>
@@ -1103,23 +862,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.48308</v>
+        <v>0.73909</v>
       </c>
       <c r="D22" t="n">
-        <v>15.96215</v>
+        <v>0.08157</v>
       </c>
       <c r="E22" t="n">
-        <v>16.53665</v>
+        <v>0.59351</v>
       </c>
       <c r="F22" t="n">
-        <v>21.64939</v>
+        <v>0.9648600000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>33.88892</v>
+        <v>0.11075</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.09266000000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.12736</v>
       </c>
     </row>
     <row r="23">
@@ -1129,19 +897,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.12415</v>
+        <v>0.75298</v>
       </c>
       <c r="D23" t="n">
-        <v>16.11351</v>
+        <v>0.08309</v>
       </c>
       <c r="E23" t="n">
-        <v>16.69903</v>
+        <v>0.5975</v>
       </c>
       <c r="F23" t="n">
-        <v>21.37044</v>
+        <v>0.94909</v>
       </c>
       <c r="G23" t="n">
-        <v>34.78247</v>
+        <v>0.10991</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.12807</v>
       </c>
     </row>
     <row r="24">
@@ -1151,19 +928,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.4886</v>
+        <v>0.75265</v>
       </c>
       <c r="D24" t="n">
-        <v>15.81392</v>
+        <v>0.08139</v>
       </c>
       <c r="E24" t="n">
-        <v>16.30033</v>
+        <v>0.60388</v>
       </c>
       <c r="F24" t="n">
-        <v>21.85496</v>
+        <v>0.95566</v>
       </c>
       <c r="G24" t="n">
-        <v>34.16671</v>
+        <v>0.11011</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09035</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.12574</v>
       </c>
     </row>
     <row r="25">
@@ -1173,19 +959,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.83892</v>
+        <v>0.73489</v>
       </c>
       <c r="D25" t="n">
-        <v>15.86088</v>
+        <v>0.08248</v>
       </c>
       <c r="E25" t="n">
-        <v>15.97675</v>
+        <v>0.60248</v>
       </c>
       <c r="F25" t="n">
-        <v>21.91536</v>
+        <v>0.97611</v>
       </c>
       <c r="G25" t="n">
-        <v>34.40282</v>
+        <v>0.11022</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09422</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.12809</v>
       </c>
     </row>
     <row r="26">
@@ -1195,19 +990,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.671</v>
+        <v>0.75224</v>
       </c>
       <c r="D26" t="n">
-        <v>15.83443</v>
+        <v>0.08064</v>
       </c>
       <c r="E26" t="n">
-        <v>16.18578</v>
+        <v>0.6109599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>21.57386</v>
+        <v>0.96064</v>
       </c>
       <c r="G26" t="n">
-        <v>33.82149</v>
+        <v>0.11023</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09302000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1269</v>
       </c>
     </row>
     <row r="27">
@@ -1217,19 +1021,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.81799</v>
+        <v>0.74533</v>
       </c>
       <c r="D27" t="n">
-        <v>16.32697</v>
+        <v>0.08227</v>
       </c>
       <c r="E27" t="n">
-        <v>16.25944</v>
+        <v>0.61064</v>
       </c>
       <c r="F27" t="n">
-        <v>22.48154</v>
+        <v>0.96669</v>
       </c>
       <c r="G27" t="n">
-        <v>34.4384</v>
+        <v>0.10995</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.09297999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.12603</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1052,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.84212</v>
+        <v>0.74587</v>
       </c>
       <c r="D28" t="n">
-        <v>15.84004</v>
+        <v>0.07961</v>
       </c>
       <c r="E28" t="n">
-        <v>16.59507</v>
+        <v>0.5966900000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>21.38821</v>
+        <v>0.9611</v>
       </c>
       <c r="G28" t="n">
-        <v>33.35699</v>
+        <v>0.10628</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09454</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.12617</v>
       </c>
     </row>
     <row r="29">
@@ -1261,19 +1083,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.63931</v>
+        <v>0.73102</v>
       </c>
       <c r="D29" t="n">
-        <v>16.0662</v>
+        <v>0.08232</v>
       </c>
       <c r="E29" t="n">
-        <v>16.29818</v>
+        <v>0.61474</v>
       </c>
       <c r="F29" t="n">
-        <v>21.86425</v>
+        <v>0.9571499999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>34.19261</v>
+        <v>0.10935</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09322999999999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.12975</v>
       </c>
     </row>
     <row r="30">
@@ -1283,345 +1114,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.82466</v>
+        <v>0.75162</v>
       </c>
       <c r="D30" t="n">
-        <v>16.0388</v>
+        <v>0.08302</v>
       </c>
       <c r="E30" t="n">
-        <v>16.36107</v>
+        <v>0.59581</v>
       </c>
       <c r="F30" t="n">
-        <v>21.29294</v>
+        <v>0.94706</v>
       </c>
       <c r="G30" t="n">
-        <v>34.0045</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.74703</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.08064</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.6137899999999999</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.94579</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.10937</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12431</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.75146</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.07993</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.59876</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.93489</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.1091</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00745</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09279999999999999</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.12695</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.7522</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.08005</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.62669</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.96756</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.10826</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09147</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.12457</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.75637</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.07965</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.60412</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.95688</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.10783</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.08998</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.1265</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.74604</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.08028</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.58833</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.9609</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.10849</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09215</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.12536</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.76414</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.08179</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.58978</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.9767400000000001</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.10872</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00749</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.0951</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.12763</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.73756</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.07965</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.61009</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.95257</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.11001</v>
-      </c>
-      <c r="H38" t="n">
+        <v>0.11128</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.00756</v>
       </c>
-      <c r="I38" t="n">
-        <v>0.09447999999999999</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.12608</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.7448399999999999</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.08177</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.59733</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.95029</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.10972</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09563000000000001</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.12715</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.71605</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.08141</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.62107</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.95752</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.11049</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00745</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.09225999999999999</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12886</v>
+      <c r="I30" t="n">
+        <v>0.09297</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.12662</v>
       </c>
     </row>
   </sheetData>
